--- a/artfynd/A 58684-2025 artfynd.xlsx
+++ b/artfynd/A 58684-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129990115</v>
       </c>
       <c r="B2" t="n">
-        <v>97668</v>
+        <v>97671</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>129990118</v>
       </c>
       <c r="B3" t="n">
-        <v>105860</v>
+        <v>105863</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>129990116</v>
       </c>
       <c r="B4" t="n">
-        <v>97668</v>
+        <v>97671</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>129990114</v>
       </c>
       <c r="B5" t="n">
-        <v>97665</v>
+        <v>97668</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 58684-2025 artfynd.xlsx
+++ b/artfynd/A 58684-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129990115</v>
       </c>
       <c r="B2" t="n">
-        <v>97671</v>
+        <v>97672</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>129990118</v>
       </c>
       <c r="B3" t="n">
-        <v>105863</v>
+        <v>105864</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>129990116</v>
       </c>
       <c r="B4" t="n">
-        <v>97671</v>
+        <v>97672</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>129990114</v>
       </c>
       <c r="B5" t="n">
-        <v>97668</v>
+        <v>97669</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 58684-2025 artfynd.xlsx
+++ b/artfynd/A 58684-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129990115</v>
       </c>
       <c r="B2" t="n">
-        <v>97672</v>
+        <v>97689</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>129990118</v>
       </c>
       <c r="B3" t="n">
-        <v>105864</v>
+        <v>105881</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>129990116</v>
       </c>
       <c r="B4" t="n">
-        <v>97672</v>
+        <v>97689</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>129990114</v>
       </c>
       <c r="B5" t="n">
-        <v>97669</v>
+        <v>97686</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 58684-2025 artfynd.xlsx
+++ b/artfynd/A 58684-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129990115</v>
       </c>
       <c r="B2" t="n">
-        <v>97705</v>
+        <v>97707</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>129990118</v>
       </c>
       <c r="B3" t="n">
-        <v>105897</v>
+        <v>105900</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>129990116</v>
       </c>
       <c r="B4" t="n">
-        <v>97705</v>
+        <v>97707</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>129990114</v>
       </c>
       <c r="B5" t="n">
-        <v>97702</v>
+        <v>97704</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 58684-2025 artfynd.xlsx
+++ b/artfynd/A 58684-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129990115</v>
       </c>
       <c r="B2" t="n">
-        <v>97707</v>
+        <v>97794</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>129990118</v>
       </c>
       <c r="B3" t="n">
-        <v>105900</v>
+        <v>105987</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -908,7 +908,7 @@
         <v>129990116</v>
       </c>
       <c r="B4" t="n">
-        <v>97707</v>
+        <v>97794</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>129990114</v>
       </c>
       <c r="B5" t="n">
-        <v>97704</v>
+        <v>97791</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
